--- a/SWTest/Outputs/Nebula_Galaxy_Analysis20250806_181111.xlsx
+++ b/SWTest/Outputs/Nebula_Galaxy_Analysis20250806_181111.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FB3979-C559-4012-A897-EA4831F86553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C43AD7-FB06-422C-AB6F-538EA61E462C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28815" yWindow="-6450" windowWidth="16005" windowHeight="18210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
